--- a/测试集/边缘情况/隐藏Sheet.xlsx
+++ b/测试集/边缘情况/隐藏Sheet.xlsx
@@ -472,103 +472,103 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46306</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>碎纸机</t>
+          <t>激光打印机</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1198</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46306</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>碎纸机</t>
+          <t>激光打印机</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1198</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>白板(块)</t>
+          <t>激光打印机</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>149</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46297</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>白板(块)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2598</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>白板笔(盒)</t>
+          <t>硒鼓</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>碎纸机</t>
+          <t>激光打印机</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>30.5</v>
@@ -584,18 +584,18 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>签字笔(盒)</t>
+          <t>文件夹(包)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/测试集/边缘情况/隐藏Sheet.xlsx
+++ b/测试集/边缘情况/隐藏Sheet.xlsx
@@ -472,82 +472,82 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46285</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>硒鼓</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2598</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>白板笔(盒)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1299</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46298</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>文件夹(包)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1299</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>白板(块)</t>
+          <t>签字笔(盒)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>298</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>硒鼓</t>
+          <t>A4打印纸(箱)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>388</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="7">
@@ -556,46 +556,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>白板笔(盒)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2598</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46307</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>白板笔(盒)</t>
+          <t>文件夹(包)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>30.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>文件夹(包)</t>
+          <t>订书机</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
